--- a/artfynd/A 44281-2024 artfynd.xlsx
+++ b/artfynd/A 44281-2024 artfynd.xlsx
@@ -954,7 +954,7 @@
         <v>131124849</v>
       </c>
       <c r="B4" t="n">
-        <v>8261</v>
+        <v>8263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44281-2024 artfynd.xlsx
+++ b/artfynd/A 44281-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130159197</v>
+        <v>131124909</v>
       </c>
       <c r="B2" t="n">
-        <v>9157</v>
+        <v>6284</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103814</v>
+        <v>100524</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläckstumpbagge</t>
+          <t>Skrovlig flatbagge</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Margarinotus purpurascens</t>
+          <t>Calitys scabra</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Herbst, 1792)</t>
+          <t>(Thunberg, 1784)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -761,17 +761,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>IBLfälla</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,31 +779,17 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>produktionsskog</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>produktionsskog</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>Hans-Erik Wanntorp</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Hans-Erik Wanntorp</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
+      <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
           <t>Hans-Erik Wanntorp</t>
@@ -826,7 +807,7 @@
         <v>130363046</v>
       </c>
       <c r="B3" t="n">
-        <v>10013</v>
+        <v>10017</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -954,7 +935,7 @@
         <v>131124849</v>
       </c>
       <c r="B4" t="n">
-        <v>8263</v>
+        <v>8265</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1086,135 +1067,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>131124909</v>
-      </c>
-      <c r="B5" t="n">
-        <v>6282</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>100524</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Skrovlig flatbagge</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Calitys scabra</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Thunberg, 1784)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>fönsterfälla</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Fäbodsberget, N, Upl</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>619246</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6662712</v>
-      </c>
-      <c r="S5" t="n">
-        <v>25</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Heby</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Harbo</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2024-05-03</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2024-06-04</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>produktionsskog</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>Hans-Erik Wanntorp</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Hans-Erik Wanntorp</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Joachim Strengbom</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44281-2024 artfynd.xlsx
+++ b/artfynd/A 44281-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -801,6 +806,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131124909</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -929,6 +939,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130363046</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1067,8 +1082,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131124849</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>